--- a/Result/profitability/1409.xlsx
+++ b/Result/profitability/1409.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27125</v>
+        <v>0.3275</v>
       </c>
       <c r="N2" t="n">
-        <v>19.9325</v>
+        <v>21.4175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.225</v>
+        <v>0.295</v>
       </c>
       <c r="N3" t="n">
-        <v>18.88</v>
+        <v>19.92</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.22125</v>
+        <v>0.28875</v>
       </c>
       <c r="N4" t="n">
-        <v>17.55</v>
+        <v>18.9725</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.16125</v>
+        <v>0.26875</v>
       </c>
       <c r="N5" t="n">
-        <v>15.7775</v>
+        <v>17.41875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0.1775</v>
       </c>
       <c r="N6" t="n">
-        <v>15.0825</v>
+        <v>15.7325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0925</v>
+        <v>0.16375</v>
       </c>
       <c r="N7" t="n">
-        <v>13.30375</v>
+        <v>14.17125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.135</v>
       </c>
       <c r="N8" t="n">
-        <v>12.26375</v>
+        <v>13.01875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11758</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8184</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3574</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2210</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-165</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2045</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1266</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.53875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.025641025641026</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2479474548440066</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-12.28571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.7602779386218876</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
